--- a/payment_forms/049_donate_for_education_using_e_check_net--payment_forms.xlsx
+++ b/payment_forms/049_donate_for_education_using_e_check_net--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>payment_forms</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Payment Forms</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>e_check_net</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>E Check Net</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>transfer_funds_so</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Transfer Funds So</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>your_sponsor_can_donate_quickly</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>your sponsor can donate quickly</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
